--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2838-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2838-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59FFB62D-4FC9-4B3E-8C02-160FCC2C0E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D586C457-7C64-4884-86E0-C7AE0435C446}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{585FB172-7A1A-4137-B3B0-A3917D50FFBC}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{2F8B2519-CB43-4E0A-B7F9-BB359910B24C}"/>
   </bookViews>
   <sheets>
     <sheet name="2838-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1520,29 +1520,29 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04882FA1-D73A-411F-927E-4E7D1B94EAD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9CDC8A-349B-412B-9799-40704C8FA1E0}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="6" width="6.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.75" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="6" width="5.88671875" customWidth="1"/>
+    <col min="7" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -1576,7 +1576,7 @@
       <c r="W1" s="30"/>
       <c r="X1" s="22"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
@@ -1612,7 +1612,7 @@
       <c r="W2" s="32"/>
       <c r="X2" s="33"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="23" t="s">
         <v>2</v>
       </c>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X3" s="36"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="25"/>
       <c r="B4" s="26"/>
       <c r="C4" s="7"/>
@@ -1732,7 +1732,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>2024</v>
       </c>
@@ -1804,7 +1804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="39">
         <v>2023</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>6.55</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2022</v>
       </c>
@@ -1948,7 +1948,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>31</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="39">
         <v>2021</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>31</v>
       </c>
@@ -2168,7 +2168,7 @@
         <v>8.59</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>31</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>2020</v>
       </c>
@@ -2314,7 +2314,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>31</v>
       </c>
@@ -2388,7 +2388,7 @@
         <v>6.13</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="11" t="s">
         <v>31</v>
       </c>
@@ -2462,7 +2462,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="39">
         <v>2019</v>
       </c>
@@ -2534,7 +2534,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="15" t="s">
         <v>31</v>
       </c>
@@ -2608,7 +2608,7 @@
         <v>9.3000000000000007</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>31</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>2018</v>
       </c>
@@ -2754,7 +2754,7 @@
         <v>7.42</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="39">
         <v>2017</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>7.75</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>2016</v>
       </c>
@@ -2898,7 +2898,7 @@
         <v>5.0999999999999996</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="39">
         <v>2015</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>4.7300000000000004</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2014</v>
       </c>
@@ -3042,7 +3042,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="39">
         <v>2013</v>
       </c>
@@ -3114,7 +3114,7 @@
         <v>10.3</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>2012</v>
       </c>
@@ -3186,7 +3186,7 @@
         <v>8.9</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="39">
         <v>2011</v>
       </c>
@@ -3258,7 +3258,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>2010</v>
       </c>
@@ -3330,7 +3330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="39">
         <v>2009</v>
       </c>
@@ -3402,7 +3402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2008</v>
       </c>
@@ -3474,7 +3474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="39">
         <v>2007</v>
       </c>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2006</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="39">
         <v>2005</v>
       </c>
@@ -3690,7 +3690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2004</v>
       </c>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="39">
         <v>2003</v>
       </c>
@@ -3834,7 +3834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2002</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="39">
         <v>2001</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2000</v>
       </c>
@@ -4050,7 +4050,7 @@
         <v>4.4400000000000004</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="39">
         <v>1999</v>
       </c>
@@ -4122,7 +4122,7 @@
         <v>11.2</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1998</v>
       </c>
@@ -4194,7 +4194,7 @@
         <v>6.09</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="39">
         <v>1997</v>
       </c>
@@ -4266,7 +4266,7 @@
         <v>6.17</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1996</v>
       </c>
@@ -4338,7 +4338,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="39">
         <v>1995</v>
       </c>
@@ -4410,7 +4410,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1994</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="39">
         <v>1993</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1992</v>
       </c>
@@ -4626,7 +4626,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="39" t="s">
         <v>59</v>
       </c>
